--- a/tenant_application_forms/048_tenant_screening_form--tenant_application_forms.xlsx
+++ b/tenant_application_forms/048_tenant_screening_form--tenant_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,8 +819,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employed',_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Employed', 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed',_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed', 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'student',_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Student', 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'disabled',_'label':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Disabled', 'label': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'w2',_'label':_'w2'}</t>
+          <t>w2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'W2', 'label': 'W2'}</t>
+          <t>W2</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'w4',_'label':_'w4'}</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'W4', 'label': 'W4'}</t>
+          <t>W4</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'bi-weekly',_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Bi-Weekly', 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'annual',_'label':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Annual', 'label': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
